--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_True.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_True.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\MinMax\scripts\comparison\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CB747F-1632-42F8-9600-F9C79EB1894E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -124,8 +118,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,21 +182,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -240,7 +226,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -274,7 +260,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -309,10 +294,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -485,16 +469,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="24.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -511,41 +490,41 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1.054969965480268E-3</v>
+        <v>0.001054969965480268</v>
       </c>
       <c r="C2">
-        <v>1.469288545195013E-4</v>
+        <v>0.0001469288545195013</v>
       </c>
       <c r="D2">
-        <v>1.12441681267228E-4</v>
+        <v>0.000112441681267228</v>
       </c>
       <c r="E2">
-        <v>1.12441681267228E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.000112441681267228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.507208775728941E-2</v>
+        <v>0.01507208775728941</v>
       </c>
       <c r="C3">
-        <v>3.4775736276060338E-3</v>
+        <v>0.003477573627606034</v>
       </c>
       <c r="D3">
-        <v>1.255041104741395E-3</v>
+        <v>0.001255041104741395</v>
       </c>
       <c r="E3">
-        <v>1.255041104741395E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.001255041104741395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -562,41 +541,41 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>7.9161388566717505E-4</v>
+        <v>0.0007916138856671751</v>
       </c>
       <c r="C5">
-        <v>1.465785171603784E-4</v>
+        <v>0.0001465785171603784</v>
       </c>
       <c r="D5">
-        <v>1.1402300879126411E-4</v>
+        <v>0.0001140230087912641</v>
       </c>
       <c r="E5">
-        <v>1.1402300879126411E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0001140230087912641</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.35308307409286499</v>
+        <v>0.353083074092865</v>
       </c>
       <c r="C6">
-        <v>4.3644462712109089E-3</v>
+        <v>0.004364446271210909</v>
       </c>
       <c r="D6">
-        <v>4.3190197902731597E-4</v>
+        <v>0.000431901979027316</v>
       </c>
       <c r="E6">
-        <v>4.3190197902731597E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.000431901979027316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -613,24 +592,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>2.6694926253032999E-16</v>
+        <v>2.6694926253033E-16</v>
       </c>
       <c r="C8">
-        <v>2.6694926253032999E-16</v>
+        <v>2.6694926253033E-16</v>
       </c>
       <c r="D8">
-        <v>2.6694926253032999E-16</v>
+        <v>2.6694926253033E-16</v>
       </c>
       <c r="E8">
-        <v>2.6694926253032999E-16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>2.6694926253033E-16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -647,7 +626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -655,166 +634,166 @@
         <v>0.3537909984588623</v>
       </c>
       <c r="C10">
-        <v>4.3708235025405884E-3</v>
+        <v>0.004370823502540588</v>
       </c>
       <c r="D10">
-        <v>4.3294025817885989E-4</v>
+        <v>0.0004329402581788599</v>
       </c>
       <c r="E10">
-        <v>4.3294025817885989E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0004329402581788599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1.5965755455659581E-17</v>
+        <v>1.596575545565958E-17</v>
       </c>
       <c r="C11">
-        <v>1.5965755455659581E-17</v>
+        <v>1.596575545565958E-17</v>
       </c>
       <c r="D11">
-        <v>1.5965755455659581E-17</v>
+        <v>1.596575545565958E-17</v>
       </c>
       <c r="E11">
-        <v>1.5965755455659581E-17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1.596575545565958E-17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>1.031687948852777E-2</v>
+        <v>0.01031687948852777</v>
       </c>
       <c r="C12">
-        <v>8.4184444858692586E-5</v>
+        <v>8.418444485869259E-05</v>
       </c>
       <c r="D12">
-        <v>2.552624391682912E-5</v>
+        <v>2.552624391682912E-05</v>
       </c>
       <c r="E12">
-        <v>2.552624391682912E-5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>2.552624391682912E-05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>8.7708320617675781</v>
+        <v>8.770832061767578</v>
       </c>
       <c r="C13">
         <v>0.1115621030330658</v>
       </c>
       <c r="D13">
-        <v>9.7425151616334915E-3</v>
+        <v>0.009742515161633492</v>
       </c>
       <c r="E13">
-        <v>9.7425151616334915E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.009742515161633492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B14">
-        <v>7.332904264330864E-3</v>
+        <v>0.007332904264330864</v>
       </c>
       <c r="C14">
-        <v>1.260066637769341E-3</v>
+        <v>0.001260066637769341</v>
       </c>
       <c r="D14">
-        <v>5.9446640079841018E-4</v>
+        <v>0.0005944664007984102</v>
       </c>
       <c r="E14">
-        <v>5.9446640079841018E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0005944664007984102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <v>7.2881910018622884E-3</v>
+        <v>0.007288191001862288</v>
       </c>
       <c r="C15">
-        <v>1.2502138270065191E-3</v>
+        <v>0.001250213827006519</v>
       </c>
       <c r="D15">
-        <v>5.8657600311562419E-4</v>
+        <v>0.0005865760031156242</v>
       </c>
       <c r="E15">
-        <v>5.8657600311562419E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.0005865760031156242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.16393749415874481</v>
+        <v>0.1639374941587448</v>
       </c>
       <c r="C16">
-        <v>3.7225432693958282E-2</v>
+        <v>0.03722543269395828</v>
       </c>
       <c r="D16">
-        <v>8.6899213492870331E-3</v>
+        <v>0.008689921349287033</v>
       </c>
       <c r="E16">
-        <v>8.6899213492870331E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.008689921349287033</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>1.7710952088236809E-2</v>
+        <v>0.01771095208823681</v>
       </c>
       <c r="C17">
-        <v>4.4053918682038784E-3</v>
+        <v>0.004405391868203878</v>
       </c>
       <c r="D17">
-        <v>1.2900182045996189E-3</v>
+        <v>0.001290018204599619</v>
       </c>
       <c r="E17">
-        <v>1.2900182045996189E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.001290018204599619</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B18">
-        <v>0.92800480127334595</v>
+        <v>0.9280048012733459</v>
       </c>
       <c r="C18">
-        <v>1.285498030483723E-2</v>
+        <v>0.01285498030483723</v>
       </c>
       <c r="D18">
-        <v>1.0650062467902901E-3</v>
+        <v>0.00106500624679029</v>
       </c>
       <c r="E18">
-        <v>1.0650062467902901E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.00106500624679029</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.93316072225570679</v>
+        <v>0.9331607222557068</v>
       </c>
       <c r="C19">
-        <v>1.2566447257995611E-2</v>
+        <v>0.01256644725799561</v>
       </c>
       <c r="D19">
-        <v>1.0255281813442709E-3</v>
+        <v>0.001025528181344271</v>
       </c>
       <c r="E19">
-        <v>1.0255281813442709E-3</v>
+        <v>0.001025528181344271</v>
       </c>
     </row>
   </sheetData>

--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_True.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_1000_True.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Pg Vm Projection True</t>
   </si>
@@ -34,85 +34,91 @@
     <t>vr_tot</t>
   </si>
   <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
     <t>solve_time</t>
   </si>
   <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
+    <t>sample_num</t>
   </si>
   <si>
     <t>qg_tot</t>
   </si>
   <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>30364.74 (26860.10 &gt; 13.54%)</t>
-  </si>
-  <si>
-    <t>1.26s (1.05 s)</t>
-  </si>
-  <si>
-    <t>1.81 (2.45)</t>
-  </si>
-  <si>
-    <t>27273.06 (26860.10 &gt; 1.53%)</t>
-  </si>
-  <si>
-    <t>0.50s (1.05 s)</t>
-  </si>
-  <si>
-    <t>2.24 (2.45)</t>
-  </si>
-  <si>
-    <t>26866.52 (26860.10 &gt; 0.02%)</t>
-  </si>
-  <si>
-    <t>1.07s (1.05 s)</t>
-  </si>
-  <si>
-    <t>2.45 (2.45)</t>
-  </si>
-  <si>
-    <t>0.81s (1.05 s)</t>
+    <t>30494.22 (27071.25 &gt; 12.64%)</t>
+  </si>
+  <si>
+    <t>183.73 (245.00)</t>
+  </si>
+  <si>
+    <t>0.09s (0.18 s)</t>
+  </si>
+  <si>
+    <t>27489.35 (27099.90 &gt; 1.44%)</t>
+  </si>
+  <si>
+    <t>225.79 (245.00)</t>
+  </si>
+  <si>
+    <t>0.13s (0.18 s)</t>
+  </si>
+  <si>
+    <t>27081.01 (27081.05 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>245.00 (245.00)</t>
+  </si>
+  <si>
+    <t>0.10s (0.18 s)</t>
+  </si>
+  <si>
+    <t>27023.69 (27023.73 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>0.11s (0.18 s)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -495,16 +501,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.001054969965480268</v>
+        <v>0.0008250387036241591</v>
       </c>
       <c r="C2">
-        <v>0.0001469288545195013</v>
+        <v>8.472910849377513E-05</v>
       </c>
       <c r="D2">
-        <v>0.000112441681267228</v>
+        <v>7.517461926909164E-05</v>
       </c>
       <c r="E2">
-        <v>0.000112441681267228</v>
+        <v>6.813493382651359E-05</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -512,33 +518,33 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.01507208775728941</v>
+        <v>0.007800679188221693</v>
       </c>
       <c r="C3">
-        <v>0.003477573627606034</v>
+        <v>0.007770427968353033</v>
       </c>
       <c r="D3">
-        <v>0.001255041104741395</v>
+        <v>0.007771008647978306</v>
       </c>
       <c r="E3">
-        <v>0.001255041104741395</v>
+        <v>0.007739113178104162</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="B4">
+        <v>0.2998214960098267</v>
+      </c>
+      <c r="C4">
+        <v>0.29502072930336</v>
+      </c>
+      <c r="D4">
+        <v>0.2940158247947693</v>
+      </c>
+      <c r="E4">
+        <v>0.2935975193977356</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -546,16 +552,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.0007916138856671751</v>
+        <v>0.9401673674583435</v>
       </c>
       <c r="C5">
-        <v>0.0001465785171603784</v>
+        <v>0.01786581799387932</v>
       </c>
       <c r="D5">
-        <v>0.0001140230087912641</v>
+        <v>0.01352869439870119</v>
       </c>
       <c r="E5">
-        <v>0.0001140230087912641</v>
+        <v>0.0127584058791399</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,33 +569,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.353083074092865</v>
+        <v>0.9280899167060852</v>
       </c>
       <c r="C6">
-        <v>0.004364446271210909</v>
+        <v>0.01640938594937325</v>
       </c>
       <c r="D6">
-        <v>0.000431901979027316</v>
+        <v>0.01284998841583729</v>
       </c>
       <c r="E6">
-        <v>0.000431901979027316</v>
+        <v>0.01212636101990938</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
+      <c r="B7">
+        <v>0.006973454263061285</v>
+      </c>
+      <c r="C7">
+        <v>0.006172064691781998</v>
+      </c>
+      <c r="D7">
+        <v>0.006761148106306791</v>
+      </c>
+      <c r="E7">
+        <v>0.006203891709446907</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,33 +603,33 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>2.6694926253033E-16</v>
+        <v>0.0003613598819356412</v>
       </c>
       <c r="C8">
-        <v>2.6694926253033E-16</v>
+        <v>0.0003547449596226215</v>
       </c>
       <c r="D8">
-        <v>2.6694926253033E-16</v>
+        <v>0.0003648692218121141</v>
       </c>
       <c r="E8">
-        <v>2.6694926253033E-16</v>
+        <v>0.0003451874945312738</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
+      <c r="B9">
+        <v>0.01055856887251139</v>
+      </c>
+      <c r="C9">
+        <v>0.0001213657669723034</v>
+      </c>
+      <c r="D9">
+        <v>0.0001317269343417138</v>
+      </c>
+      <c r="E9">
+        <v>0.0001247773034265265</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -631,33 +637,33 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.3537909984588623</v>
+        <v>8.859152793884277</v>
       </c>
       <c r="C10">
-        <v>0.004370823502540588</v>
+        <v>0.2175999283790588</v>
       </c>
       <c r="D10">
-        <v>0.0004329402581788599</v>
+        <v>0.1617692559957504</v>
       </c>
       <c r="E10">
-        <v>0.0004329402581788599</v>
+        <v>0.1503901332616806</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <v>1.596575545565958E-17</v>
-      </c>
-      <c r="C11">
-        <v>1.596575545565958E-17</v>
-      </c>
-      <c r="D11">
-        <v>1.596575545565958E-17</v>
-      </c>
-      <c r="E11">
-        <v>1.596575545565958E-17</v>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -665,16 +671,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.01031687948852777</v>
+        <v>0.0006000705761834979</v>
       </c>
       <c r="C12">
-        <v>8.418444485869259E-05</v>
+        <v>8.357510523637757E-05</v>
       </c>
       <c r="D12">
-        <v>2.552624391682912E-05</v>
+        <v>6.719108205288649E-05</v>
       </c>
       <c r="E12">
-        <v>2.552624391682912E-05</v>
+        <v>6.092254625400528E-05</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -682,16 +688,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>8.770832061767578</v>
+        <v>0.3002616763114929</v>
       </c>
       <c r="C13">
-        <v>0.1115621030330658</v>
+        <v>0.2954728305339813</v>
       </c>
       <c r="D13">
-        <v>0.009742515161633492</v>
+        <v>0.2944690585136414</v>
       </c>
       <c r="E13">
-        <v>0.009742515161633492</v>
+        <v>0.2940488755702972</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,33 +705,33 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.007332904264330864</v>
+        <v>0.01962132751941681</v>
       </c>
       <c r="C14">
-        <v>0.001260066637769341</v>
+        <v>0.008159850724041462</v>
       </c>
       <c r="D14">
-        <v>0.0005944664007984102</v>
+        <v>0.003362692194059491</v>
       </c>
       <c r="E14">
-        <v>0.0005944664007984102</v>
+        <v>0.003179313149303198</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
-        <v>0.007288191001862288</v>
-      </c>
-      <c r="C15">
-        <v>0.001250213827006519</v>
-      </c>
-      <c r="D15">
-        <v>0.0005865760031156242</v>
-      </c>
-      <c r="E15">
-        <v>0.0005865760031156242</v>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,16 +739,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.1639374941587448</v>
+        <v>0.007139887195080519</v>
       </c>
       <c r="C16">
-        <v>0.03722543269395828</v>
+        <v>0.007117151748389006</v>
       </c>
       <c r="D16">
-        <v>0.008689921349287033</v>
+        <v>0.007112820632755756</v>
       </c>
       <c r="E16">
-        <v>0.008689921349287033</v>
+        <v>0.007084198761731386</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,50 +756,55 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.01771095208823681</v>
+        <v>0.007950017228722572</v>
       </c>
       <c r="C17">
-        <v>0.004405391868203878</v>
+        <v>0.005452282726764679</v>
       </c>
       <c r="D17">
-        <v>0.001290018204599619</v>
+        <v>0.002647274173796177</v>
       </c>
       <c r="E17">
-        <v>0.001290018204599619</v>
+        <v>0.002519241999834776</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0.9280048012733459</v>
-      </c>
-      <c r="C18">
-        <v>0.01285498030483723</v>
-      </c>
-      <c r="D18">
-        <v>0.00106500624679029</v>
-      </c>
-      <c r="E18">
-        <v>0.00106500624679029</v>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>0.9331607222557068</v>
-      </c>
-      <c r="C19">
-        <v>0.01256644725799561</v>
-      </c>
-      <c r="D19">
-        <v>0.001025528181344271</v>
-      </c>
-      <c r="E19">
-        <v>0.001025528181344271</v>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.186325877904892</v>
+      </c>
+      <c r="C20">
+        <v>0.07679746299982071</v>
+      </c>
+      <c r="D20">
+        <v>0.03407091647386551</v>
+      </c>
+      <c r="E20">
+        <v>0.03219429403543472</v>
       </c>
     </row>
   </sheetData>
